--- a/Misc/Simple Portfolio Model.xlsx
+++ b/Misc/Simple Portfolio Model.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jlaya\Downloads\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3d81ccc39c065ba0/Documents/Personal Development/Postgrad/UNSW/Data Science/07. Multivariate Statistics/Neural_Lace_MvS/Misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729F0B52-E111-4994-9530-5778029ADBF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="261" documentId="13_ncr:1_{729F0B52-E111-4994-9530-5778029ADBF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E79AC20-3155-4B15-9C4C-1C310C472F77}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{78ED9877-80C6-4688-9764-79F8ED95C0F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
   <si>
     <t>Asset Class</t>
   </si>
@@ -99,19 +99,37 @@
     <t>Correlation Matrix</t>
   </si>
   <si>
-    <t>Returns and Volatility</t>
-  </si>
-  <si>
-    <t>Formula for Expected Return and Variance</t>
-  </si>
-  <si>
     <t>https://edstem.org/au/courses/41412/lessons/119133/slides/817744</t>
   </si>
   <si>
-    <t>Expected Return</t>
-  </si>
-  <si>
-    <t>Expected Volatility</t>
+    <t>6 variance terms plus 15 covariance pairs (C(6,2) = 15). Each pair is doubled because the matrix is symmetric.</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>1)</t>
+  </si>
+  <si>
+    <t>2)</t>
+  </si>
+  <si>
+    <t>Variance for 2 Assets - this is what we have in Ed:</t>
+  </si>
+  <si>
+    <t>This is what we normally use to calculate variance for 6 Assets:</t>
+  </si>
+  <si>
+    <t>Return</t>
+  </si>
+  <si>
+    <t>Capital Market Assumptions</t>
+  </si>
+  <si>
+    <t>Expected Portfolio Performance</t>
+  </si>
+  <si>
+    <t>Notes on portfolio variance</t>
   </si>
 </sst>
 </file>
@@ -121,9 +139,9 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00_ ;[Red]\(#,##0.00\)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,13 +165,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -161,8 +172,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,8 +220,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -192,14 +237,88 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.14996795556505021"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.14996795556505021"/>
       </right>
       <top style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
       </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -210,29 +329,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -259,21 +400,21 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>457874</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>160367</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>518160</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>103750</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="11" name="Picture 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2D93078-A8C6-C7E6-31D2-2F41F69AA690}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE10AC37-2450-46D1-A624-35F5785FD178}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -289,8 +430,96 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13152120" y="365760"/>
-          <a:ext cx="7773074" cy="4008467"/>
+          <a:off x="13060680" y="2484120"/>
+          <a:ext cx="6614160" cy="3410830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>495607</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>38151</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDB07B99-73CE-490B-AFE7-20AF8FD59D5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13060680" y="6156960"/>
+          <a:ext cx="3543607" cy="586791"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>457662</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>38230</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D516C0E6-6C71-42E0-9AA7-D1E7F870C5B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13060680" y="7071360"/>
+          <a:ext cx="5334462" cy="1501270"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -619,350 +848,405 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{301AB51D-D904-4091-AC2D-FDB11BC2BA70}">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="8.88671875" customWidth="1"/>
-    <col min="9" max="9" width="38.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="38.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="8.88671875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="38.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="9"/>
+    <col min="9" max="11" width="8.88671875" style="9" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" style="9"/>
+    <col min="13" max="14" width="3.77734375" style="9" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+    </row>
+    <row r="2" spans="1:25" ht="111.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="15">
+        <v>7.3516781267455242E-2</v>
+      </c>
+      <c r="C3" s="15">
+        <v>0.1535787290193211</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="17">
+        <v>1</v>
+      </c>
+      <c r="G3" s="18">
+        <v>0.53477428116850767</v>
+      </c>
+      <c r="H3" s="18">
+        <v>0.77957417439569665</v>
+      </c>
+      <c r="I3" s="18">
+        <v>2.057429493367504E-2</v>
+      </c>
+      <c r="J3" s="18">
+        <v>6.7194520069264907E-2</v>
+      </c>
+      <c r="K3" s="18">
+        <v>3.1729991894188472E-2</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>6.5531994237576024E-2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.14393036262553441</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0.53477428116850756</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0.66056758432234219</v>
+      </c>
+      <c r="I4" s="6">
+        <v>9.2844962625703714E-2</v>
+      </c>
+      <c r="J4" s="6">
+        <v>5.1932359070597624E-3</v>
+      </c>
+      <c r="K4" s="6">
+        <v>2.1878821709088041E-2</v>
+      </c>
+      <c r="O4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="6" t="s">
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>6.4863723566813386E-2</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.1583596025732435</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0.77957417439569665</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0.66056758432234219</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="6">
+        <v>-4.7236410210640727E-2</v>
+      </c>
+      <c r="J5" s="6">
+        <v>1.7739321347426281E-2</v>
+      </c>
+      <c r="K5" s="6">
+        <v>-4.3395986999765932E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>4.2614663370993247E-2</v>
+      </c>
+      <c r="C6" s="3">
+        <v>4.2939509654822218E-2</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="6">
+        <v>2.0574294933675061E-2</v>
+      </c>
+      <c r="G6" s="6">
+        <v>9.2844962625703673E-2</v>
+      </c>
+      <c r="H6" s="6">
+        <v>-4.7236410210640727E-2</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0.76686362852933843</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0.48839812538776578</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3">
+        <v>4.5459342349806482E-2</v>
+      </c>
+      <c r="C7" s="3">
+        <v>4.2180197994448262E-2</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="6">
+        <v>6.7194520069264907E-2</v>
+      </c>
+      <c r="G7" s="6">
+        <v>5.1932359070597459E-3</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1.7739321347426281E-2</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.76686362852933843</v>
+      </c>
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0.48935992304180898</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3">
+        <v>3.8421247837531217E-2</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1.754830916915685E-2</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
+        <v>3.1729991894188479E-2</v>
+      </c>
+      <c r="G8" s="6">
+        <v>2.1878821709088021E-2</v>
+      </c>
+      <c r="H8" s="6">
+        <v>-4.3395986999766011E-3</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.48839812538776578</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0.48935992304180898</v>
+      </c>
+      <c r="K8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="K9" s="13"/>
+    </row>
+    <row r="11" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="O1" t="s">
+      <c r="B11" s="22"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="25">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.21000000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="2">
+        <f>SUM(B14:B19)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="22"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="24" cm="1">
+        <f t="array" ref="B24">SUMPRODUCT(B3:B8, _xlfn.XLOOKUP(A3:A8, A14:A19, B14:B19))</f>
+        <v>6.1071173754798605E-2</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="23" cm="1">
+        <f t="array" ref="B25">SQRT(MMULT(TRANSPOSE(B14:B19*C3:C8),MMULT(F3:K8,B14:B19*C3:C8)))</f>
+        <v>9.4722648534133883E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O29" s="9" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O2" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2">
-        <v>7.3516781267455242E-2</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.1535787290193211</v>
-      </c>
-      <c r="I4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2">
-        <v>6.5531994237576024E-2</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.14393036262553441</v>
-      </c>
-      <c r="I5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0.21000000000000002</v>
-      </c>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2">
-        <v>6.4863723566813386E-2</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.1583596025732435</v>
-      </c>
-      <c r="I6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2">
-        <v>4.2614663370993247E-2</v>
-      </c>
-      <c r="C7" s="2">
-        <v>4.2939509654822218E-2</v>
-      </c>
-      <c r="I7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0.125</v>
-      </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2">
-        <v>4.5459342349806482E-2</v>
-      </c>
-      <c r="C8" s="2">
-        <v>4.2180197994448262E-2</v>
-      </c>
-      <c r="I8" t="s">
-        <v>6</v>
-      </c>
-      <c r="J8" s="1">
-        <v>0.125</v>
-      </c>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2">
-        <v>3.8421247837531217E-2</v>
-      </c>
-      <c r="C9" s="2">
-        <v>1.754830916915685E-2</v>
-      </c>
-      <c r="I9" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="J10" s="1">
-        <f>SUM(J4:J9)</f>
-        <v>1</v>
-      </c>
-      <c r="K10" s="9"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="10" cm="1">
-        <f t="array" ref="J12">SUMPRODUCT(B4:B9, _xlfn.XLOOKUP(A4:A9, I4:I9, J4:J9))</f>
-        <v>6.1071173754798605E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="I13" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="11"/>
-    </row>
-    <row r="14" spans="1:15" ht="130.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="3">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4">
-        <v>0.53477428116850767</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0.77957417439569665</v>
-      </c>
-      <c r="E15" s="4">
-        <v>2.057429493367504E-2</v>
-      </c>
-      <c r="F15" s="4">
-        <v>6.7194520069264907E-2</v>
-      </c>
-      <c r="G15" s="4">
-        <v>3.1729991894188472E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="4">
-        <v>0.53477428116850756</v>
-      </c>
-      <c r="C16" s="3">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0.66056758432234219</v>
-      </c>
-      <c r="E16" s="4">
-        <v>9.2844962625703714E-2</v>
-      </c>
-      <c r="F16" s="4">
-        <v>5.1932359070597624E-3</v>
-      </c>
-      <c r="G16" s="4">
-        <v>2.1878821709088041E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="4">
-        <v>0.77957417439569665</v>
-      </c>
-      <c r="C17" s="4">
-        <v>0.66056758432234219</v>
-      </c>
-      <c r="D17" s="3">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4">
-        <v>-4.7236410210640727E-2</v>
-      </c>
-      <c r="F17" s="4">
-        <v>1.7739321347426281E-2</v>
-      </c>
-      <c r="G17" s="4">
-        <v>-4.3395986999765932E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="4">
-        <v>2.0574294933675061E-2</v>
-      </c>
-      <c r="C18" s="4">
-        <v>9.2844962625703673E-2</v>
-      </c>
-      <c r="D18" s="4">
-        <v>-4.7236410210640727E-2</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1</v>
-      </c>
-      <c r="F18" s="4">
-        <v>0.76686362852933843</v>
-      </c>
-      <c r="G18" s="4">
-        <v>0.48839812538776578</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="4">
-        <v>6.7194520069264907E-2</v>
-      </c>
-      <c r="C19" s="4">
-        <v>5.1932359070597459E-3</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1.7739321347426281E-2</v>
-      </c>
-      <c r="E19" s="4">
-        <v>0.76686362852933843</v>
-      </c>
-      <c r="F19" s="3">
-        <v>1</v>
-      </c>
-      <c r="G19" s="4">
-        <v>0.48935992304180898</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="4">
-        <v>3.1729991894188479E-2</v>
-      </c>
-      <c r="C20" s="4">
-        <v>2.1878821709088021E-2</v>
-      </c>
-      <c r="D20" s="4">
-        <v>-4.3395986999766011E-3</v>
-      </c>
-      <c r="E20" s="4">
-        <v>0.48839812538776578</v>
-      </c>
-      <c r="F20" s="4">
-        <v>0.48935992304180898</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="O2" r:id="rId1" xr:uid="{A1D53DB6-2D7E-40AA-BB9C-339A260F4846}"/>
+    <hyperlink ref="O4" r:id="rId1" xr:uid="{A1D53DB6-2D7E-40AA-BB9C-339A260F4846}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 [SEC=GENERAL BUSINESS]</oddFooter>
   </headerFooter>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>